--- a/app-assets/templates/Mascara_Importacao_Medicoes.xlsx
+++ b/app-assets/templates/Mascara_Importacao_Medicoes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anderson.marley\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F38C7D-3333-412F-B9CD-FC93F2411281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A48995BF-8187-432B-AA53-5905F9CD3160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instruções" sheetId="1" r:id="rId1"/>
@@ -18,12 +18,25 @@
     <sheet name="MAPA PAGTO" sheetId="3" r:id="rId3"/>
     <sheet name="Documentos Auxiliares" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="75">
   <si>
     <t>Painel</t>
   </si>
@@ -100,9 +113,6 @@
     <t>Retorno Vale</t>
   </si>
   <si>
-    <t>Encerramento</t>
-  </si>
-  <si>
     <t>Arquivamento</t>
   </si>
   <si>
@@ -127,9 +137,6 @@
     <t>ATO</t>
   </si>
   <si>
-    <t>CPF / CNPJ</t>
-  </si>
-  <si>
     <t>Intr. Sossego</t>
   </si>
   <si>
@@ -202,33 +209,15 @@
     <t>Projetista</t>
   </si>
   <si>
-    <t>Função</t>
-  </si>
-  <si>
-    <t>Referência</t>
-  </si>
-  <si>
     <t>% Emissão</t>
   </si>
   <si>
-    <t>Observação</t>
-  </si>
-  <si>
     <t>Valor De Medição</t>
   </si>
   <si>
-    <t>Condição</t>
-  </si>
-  <si>
-    <t>Tipo2</t>
-  </si>
-  <si>
     <t>Responsável</t>
   </si>
   <si>
-    <t>Razão Social</t>
-  </si>
-  <si>
     <t>Valor</t>
   </si>
   <si>
@@ -236,6 +225,42 @@
   </si>
   <si>
     <t>Ciclo Retorno</t>
+  </si>
+  <si>
+    <t>Líder Responsável</t>
+  </si>
+  <si>
+    <t>Valor do Reajuste 3º</t>
+  </si>
+  <si>
+    <t>OBS</t>
+  </si>
+  <si>
+    <t>FUNÇÃO</t>
+  </si>
+  <si>
+    <t>CICLO</t>
+  </si>
+  <si>
+    <t>PROJETISTA</t>
+  </si>
+  <si>
+    <t>REFERÊNCIA</t>
+  </si>
+  <si>
+    <t>% EMISSÃO</t>
+  </si>
+  <si>
+    <t>CONTRATO</t>
+  </si>
+  <si>
+    <t>TIPO2</t>
+  </si>
+  <si>
+    <t>CONDIÇÃO</t>
+  </si>
+  <si>
+    <t>VALOR DE MEDIÇÃO</t>
   </si>
 </sst>
 </file>
@@ -314,38 +339,6 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
         <color auto="1"/>
         <name val="Calibri"/>
         <scheme val="none"/>
@@ -370,6 +363,38 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -384,58 +409,56 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16ABC298-D890-425A-8B83-302B4B1B4B87}" name="Tabela1" displayName="Tabela1" ref="A1:AI2" insertRow="1" totalsRowShown="0" headerRowDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16ABC298-D890-425A-8B83-302B4B1B4B87}" name="Tabela1" displayName="Tabela1" ref="A1:AI2" insertRow="1" totalsRowShown="0" headerRowDxfId="1">
   <autoFilter ref="A1:AI2" xr:uid="{16ABC298-D890-425A-8B83-302B4B1B4B87}"/>
   <tableColumns count="35">
     <tableColumn id="1" xr3:uid="{0194AA52-A628-48BF-AFB1-084E65A5183D}" name="Número da Medição"/>
     <tableColumn id="2" xr3:uid="{2E7BB03E-2BA3-4164-A49E-C7848C85DDCC}" name="Projeto Referente"/>
     <tableColumn id="3" xr3:uid="{8049726B-FA79-481B-B38B-D7E5C5A24E7D}" name="Título Primário"/>
     <tableColumn id="4" xr3:uid="{2528B188-9C94-4630-AC28-6291DFBC945B}" name="Centro de Custo"/>
-    <tableColumn id="5" xr3:uid="{2A800B0C-06EC-47C0-88EE-093F15FFF752}" name="Localização"/>
-    <tableColumn id="6" xr3:uid="{192268A4-BEF4-4547-9F20-57208357ACC4}" name="Contrato"/>
-    <tableColumn id="7" xr3:uid="{91709895-833D-413D-A506-EF1AE282CD06}" name="Coordenador"/>
-    <tableColumn id="8" xr3:uid="{0A150865-85A6-40DC-88AE-61FDB10FE270}" name="Projetista"/>
-    <tableColumn id="9" xr3:uid="{C5B7CF7D-9758-4CC5-9D98-68A400D7988C}" name="Função"/>
-    <tableColumn id="10" xr3:uid="{AA8C4C3A-2F3D-4A16-A793-FB433003A65D}" name="Mesclado"/>
-    <tableColumn id="11" xr3:uid="{017894F5-8A23-4F74-ADF6-AB532A1D5817}" name="Número do Documento"/>
-    <tableColumn id="12" xr3:uid="{AA0F30A3-5724-4BC5-A055-DE7E2C2F60FD}" name="Evidência"/>
-    <tableColumn id="13" xr3:uid="{F469D265-E0B9-480D-B8FE-C95FEACA0EE3}" name="Data de Cadastro"/>
-    <tableColumn id="14" xr3:uid="{BBB37DBD-6859-4449-A02F-906F36E9A1FD}" name="Formato"/>
-    <tableColumn id="15" xr3:uid="{121F15C8-31C5-490A-B47D-9BE430738EF0}" name="Quantidade"/>
-    <tableColumn id="16" xr3:uid="{71F8ECB0-4421-446A-9876-D842CF5E9FE7}" name="Multiplicador"/>
-    <tableColumn id="17" xr3:uid="{53FD36FB-FD54-4608-95CB-27CD17635930}" name="Equivalente (A1 ou Horas)"/>
-    <tableColumn id="18" xr3:uid="{C5A325E4-3B7B-490E-B559-0B8132209AC7}" name="Porcentagem de Revisão"/>
-    <tableColumn id="19" xr3:uid="{DB1B8F39-2373-4EBC-BC35-67DCDB20E0FF}" name="Emissão Inicial"/>
-    <tableColumn id="20" xr3:uid="{F1F063E7-39E0-4CE6-A0CE-ADA013776963}" name="Retorno Vale"/>
-    <tableColumn id="21" xr3:uid="{AAA66E2C-359F-483E-8244-EE4D047C3CE9}" name="Encerramento"/>
-    <tableColumn id="22" xr3:uid="{C257EE7D-7007-4A94-AEFF-CBDA87584865}" name="Arquivamento"/>
-    <tableColumn id="23" xr3:uid="{3218BCCC-166E-49C0-8976-318B59DDE656}" name="Medido (Horas)"/>
-    <tableColumn id="24" xr3:uid="{F262FF0E-EC8D-4042-9C7E-54AC1FDFC6CC}" name="Item da QQP"/>
-    <tableColumn id="25" xr3:uid="{6954D7EA-EAFB-4E8C-ADC4-59AB8D0FD8BE}" name="Valor Unitário"/>
-    <tableColumn id="26" xr3:uid="{D8CB2860-88AA-48EA-8BF5-F56093841D5C}" name="Valor Bruto"/>
-    <tableColumn id="27" xr3:uid="{FF43DFDB-72B1-400A-B051-DECF87AD2F29}" name="Valor Total"/>
-    <tableColumn id="28" xr3:uid="{77EB0AC2-FF06-4AF1-9736-DCA004EF0407}" name="Observação"/>
-    <tableColumn id="29" xr3:uid="{F069247B-C707-4C94-90DB-8615C8B05474}" name="Valor do Reajuste"/>
-    <tableColumn id="30" xr3:uid="{AFDD3155-BB6B-493A-AB0D-6A689BCEAE39}" name="Ciclo"/>
-    <tableColumn id="31" xr3:uid="{843453DA-9F88-43A4-8737-143A1EEAE927}" name="Referência"/>
-    <tableColumn id="32" xr3:uid="{3C6843AB-87BA-473C-AF93-7ED0CF3525B7}" name="% Emissão"/>
-    <tableColumn id="33" xr3:uid="{EB40C135-DDC6-4B4B-AD59-E9E80A5C6538}" name="Tipo2"/>
-    <tableColumn id="34" xr3:uid="{D81A8A93-710E-40A9-9E45-ECCB6B8CC20A}" name="Condição"/>
-    <tableColumn id="35" xr3:uid="{884B513E-F3BE-4658-99EE-50A839D5D03C}" name="Valor De Medição"/>
+    <tableColumn id="5" xr3:uid="{2A800B0C-06EC-47C0-88EE-093F15FFF752}" name="Coordenador"/>
+    <tableColumn id="6" xr3:uid="{192268A4-BEF4-4547-9F20-57208357ACC4}" name="Líder Responsável"/>
+    <tableColumn id="7" xr3:uid="{91709895-833D-413D-A506-EF1AE282CD06}" name="Número do Documento"/>
+    <tableColumn id="8" xr3:uid="{0A150865-85A6-40DC-88AE-61FDB10FE270}" name="Evidência"/>
+    <tableColumn id="9" xr3:uid="{C5B7CF7D-9758-4CC5-9D98-68A400D7988C}" name="Data de Cadastro"/>
+    <tableColumn id="10" xr3:uid="{AA8C4C3A-2F3D-4A16-A793-FB433003A65D}" name="Formato"/>
+    <tableColumn id="11" xr3:uid="{017894F5-8A23-4F74-ADF6-AB532A1D5817}" name="Quantidade"/>
+    <tableColumn id="12" xr3:uid="{AA0F30A3-5724-4BC5-A055-DE7E2C2F60FD}" name="Multiplicador"/>
+    <tableColumn id="13" xr3:uid="{F469D265-E0B9-480D-B8FE-C95FEACA0EE3}" name="Equivalente (A1 ou Horas)"/>
+    <tableColumn id="14" xr3:uid="{BBB37DBD-6859-4449-A02F-906F36E9A1FD}" name="Porcentagem de Revisão"/>
+    <tableColumn id="15" xr3:uid="{121F15C8-31C5-490A-B47D-9BE430738EF0}" name="Emissão Inicial"/>
+    <tableColumn id="16" xr3:uid="{71F8ECB0-4421-446A-9876-D842CF5E9FE7}" name="Retorno Vale"/>
+    <tableColumn id="17" xr3:uid="{53FD36FB-FD54-4608-95CB-27CD17635930}" name="Arquivamento"/>
+    <tableColumn id="18" xr3:uid="{C5A325E4-3B7B-490E-B559-0B8132209AC7}" name="Medido (Horas)"/>
+    <tableColumn id="19" xr3:uid="{DB1B8F39-2373-4EBC-BC35-67DCDB20E0FF}" name="Valor do Reajuste 3º"/>
+    <tableColumn id="20" xr3:uid="{F1F063E7-39E0-4CE6-A0CE-ADA013776963}" name="Item da QQP"/>
+    <tableColumn id="21" xr3:uid="{AAA66E2C-359F-483E-8244-EE4D047C3CE9}" name="Valor Unitário"/>
+    <tableColumn id="22" xr3:uid="{C257EE7D-7007-4A94-AEFF-CBDA87584865}" name="Valor Bruto"/>
+    <tableColumn id="23" xr3:uid="{3218BCCC-166E-49C0-8976-318B59DDE656}" name="Valor do Reajuste"/>
+    <tableColumn id="24" xr3:uid="{F262FF0E-EC8D-4042-9C7E-54AC1FDFC6CC}" name="Valor Total"/>
+    <tableColumn id="25" xr3:uid="{6954D7EA-EAFB-4E8C-ADC4-59AB8D0FD8BE}" name="OBS"/>
+    <tableColumn id="26" xr3:uid="{D8CB2860-88AA-48EA-8BF5-F56093841D5C}" name="FUNÇÃO"/>
+    <tableColumn id="27" xr3:uid="{FF43DFDB-72B1-400A-B051-DECF87AD2F29}" name="Localização"/>
+    <tableColumn id="28" xr3:uid="{77EB0AC2-FF06-4AF1-9736-DCA004EF0407}" name="CICLO"/>
+    <tableColumn id="29" xr3:uid="{F069247B-C707-4C94-90DB-8615C8B05474}" name="PROJETISTA"/>
+    <tableColumn id="30" xr3:uid="{AFDD3155-BB6B-493A-AB0D-6A689BCEAE39}" name="REFERÊNCIA"/>
+    <tableColumn id="31" xr3:uid="{843453DA-9F88-43A4-8737-143A1EEAE927}" name="% EMISSÃO"/>
+    <tableColumn id="32" xr3:uid="{3C6843AB-87BA-473C-AF93-7ED0CF3525B7}" name="CONTRATO"/>
+    <tableColumn id="33" xr3:uid="{EB40C135-DDC6-4B4B-AD59-E9E80A5C6538}" name="TIPO2"/>
+    <tableColumn id="34" xr3:uid="{D81A8A93-710E-40A9-9E45-ECCB6B8CC20A}" name="CONDIÇÃO"/>
+    <tableColumn id="35" xr3:uid="{884B513E-F3BE-4658-99EE-50A839D5D03C}" name="VALOR DE MEDIÇÃO"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CDA549AE-138C-4003-82E3-D66E90104F13}" name="Tabela2" displayName="Tabela2" ref="A1:L2" insertRow="1" totalsRowShown="0" headerRowDxfId="3">
-  <autoFilter ref="A1:L2" xr:uid="{CDA549AE-138C-4003-82E3-D66E90104F13}"/>
-  <tableColumns count="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CDA549AE-138C-4003-82E3-D66E90104F13}" name="Tabela2" displayName="Tabela2" ref="A1:J2" insertRow="1" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:J2" xr:uid="{CDA549AE-138C-4003-82E3-D66E90104F13}"/>
+  <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{D044B2A0-0518-42CC-AF75-49A9D04A907D}" name="ATO"/>
     <tableColumn id="2" xr3:uid="{C49E5E40-DDE8-4324-A87F-20859D0AFA6A}" name="Projetista"/>
     <tableColumn id="3" xr3:uid="{79C07A0A-F5F3-499F-B4C3-8E5DD6E5ABE2}" name="Responsável"/>
-    <tableColumn id="4" xr3:uid="{6D623308-00A4-4B16-97E7-A97FE0383225}" name="CPF / CNPJ"/>
-    <tableColumn id="5" xr3:uid="{28F989DE-AA1C-4B4A-8D8A-94C0CFBF86A5}" name="Razão Social"/>
     <tableColumn id="6" xr3:uid="{AB7E0A66-EE3C-4525-95F0-9473B94F6B7C}" name="Intr. Sossego"/>
     <tableColumn id="7" xr3:uid="{4A72F2EF-DD5A-442D-B3F3-E2423F5B5BCA}" name="Salobo"/>
     <tableColumn id="8" xr3:uid="{E05C0778-5BCF-4AD0-ACA4-CEBBD6024230}" name="ACG"/>
@@ -449,7 +472,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2C693005-0F0F-4735-9DB2-1CEBAD129733}" name="Tabela3" displayName="Tabela3" ref="A1:Z2" insertRow="1" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2C693005-0F0F-4735-9DB2-1CEBAD129733}" name="Tabela3" displayName="Tabela3" ref="A1:Z2" insertRow="1" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3" tableBorderDxfId="2">
   <autoFilter ref="A1:Z2" xr:uid="{2C693005-0F0F-4735-9DB2-1CEBAD129733}"/>
   <tableColumns count="26">
     <tableColumn id="1" xr3:uid="{9DEE5CB9-EDF7-42A7-A03D-4143F7362B90}" name="Projeto"/>
@@ -852,37 +875,37 @@
     <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="23.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.25">
@@ -899,97 +922,97 @@
         <v>11</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y1" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z1" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA1" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="AB1" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="AC1" s="2" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="AD1" s="2" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
       <c r="AE1" s="2" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AF1" s="2" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="AG1" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="AH1" s="2" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="AI1" s="2" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1002,29 +1025,29 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="12" width="18" customWidth="1"/>
+    <col min="4" max="10" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>35</v>
@@ -1033,19 +1056,13 @@
         <v>36</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="J1" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1089,37 +1106,37 @@
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>18</v>
@@ -1128,43 +1145,43 @@
         <v>19</v>
       </c>
       <c r="N1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="P1" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="U1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="W1" s="3" t="s">
         <v>14</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
